--- a/Result/profitability/1531.xlsx
+++ b/Result/profitability/1531.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.04125000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>19.13125</v>
+        <v>18.29</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09500000000000001</v>
+        <v>0.06125000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>19.8275</v>
+        <v>19.795</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.16125</v>
+        <v>0.13375</v>
       </c>
       <c r="N4" t="n">
-        <v>21.17125</v>
+        <v>20.54375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1425</v>
+        <v>0.20875</v>
       </c>
       <c r="N5" t="n">
-        <v>19.165</v>
+        <v>18.18875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27</v>
+        <v>0.24125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.63875</v>
+        <v>19.14125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="N7" t="n">
-        <v>19.98875</v>
+        <v>19.39125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20875</v>
+        <v>0.19875</v>
       </c>
       <c r="N8" t="n">
-        <v>20.7575</v>
+        <v>20.7625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>434</v>
+      </c>
+      <c r="D75" t="n">
+        <v>370</v>
+      </c>
+      <c r="E75" t="n">
+        <v>64</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.17%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.01750000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.2975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.002722940776038074</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9137931034482758</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.809999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3464951197870452</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
